--- a/dcf/GOOG.xlsx
+++ b/dcf/GOOG.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -1186,25 +1186,25 @@
         <v>13</v>
       </c>
       <c r="B5" s="53" t="n">
-        <v>190.50059513956</v>
+        <v>162.475430037336</v>
       </c>
       <c r="C5" s="53" t="n">
-        <v>182.7027122544771</v>
+        <v>155.8892072968742</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>175.2748967834144</v>
+        <v>149.6147858449686</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>168.1977956030614</v>
+        <v>143.6358796794079</v>
       </c>
       <c r="F5" s="53" t="n">
-        <v>161.4531552703079</v>
+        <v>137.9371275519756</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>155.0237547400807</v>
+        <v>132.5040364133848</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>148.8933424861912</v>
+        <v>127.3229285581722</v>
       </c>
     </row>
     <row r="6">
@@ -1212,25 +1212,25 @@
         <v>14</v>
       </c>
       <c r="B6" s="53" t="n">
-        <v>201.3357964109504</v>
+        <v>171.5715759304003</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>193.0505560625115</v>
+        <v>164.5762168501767</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>185.1593877781537</v>
+        <v>157.9128109498859</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>177.6416543757167</v>
+        <v>151.5639942605729</v>
       </c>
       <c r="F6" s="53" t="n">
-        <v>170.4778924328239</v>
+        <v>145.5133897570497</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>163.6497404225891</v>
+        <v>139.7455469561337</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>157.139871554662</v>
+        <v>134.2458854686515</v>
       </c>
     </row>
     <row r="7">
@@ -1238,25 +1238,25 @@
         <v>15</v>
       </c>
       <c r="B7" s="53" t="n">
-        <v>212.1709976823408</v>
+        <v>180.6677218234647</v>
       </c>
       <c r="C7" s="53" t="n">
-        <v>203.3983998705459</v>
+        <v>173.2632264034792</v>
       </c>
       <c r="D7" s="53" t="n">
-        <v>195.0438787728929</v>
+        <v>166.2108360548032</v>
       </c>
       <c r="E7" s="53" t="n">
-        <v>187.0855131483719</v>
+        <v>159.4921088417379</v>
       </c>
       <c r="F7" s="53" t="n">
-        <v>179.5026295953399</v>
+        <v>153.0896519621237</v>
       </c>
       <c r="G7" s="53" t="n">
-        <v>172.2757261050974</v>
+        <v>146.9870574988826</v>
       </c>
       <c r="H7" s="53" t="n">
-        <v>165.3864006231328</v>
+        <v>141.1688423791308</v>
       </c>
     </row>
     <row r="8">
@@ -1264,25 +1264,25 @@
         <v>16</v>
       </c>
       <c r="B8" s="53" t="n">
-        <v>223.0061989537311</v>
+        <v>189.7638677165289</v>
       </c>
       <c r="C8" s="53" t="n">
-        <v>213.7462436785803</v>
+        <v>181.9502359567817</v>
       </c>
       <c r="D8" s="53" t="n">
-        <v>204.9283697676322</v>
+        <v>174.5088611597205</v>
       </c>
       <c r="E8" s="54" t="n">
-        <v>196.5293719210271</v>
+        <v>167.4202234229029</v>
       </c>
       <c r="F8" s="53" t="n">
-        <v>188.5273667578559</v>
+        <v>160.6659141671977</v>
       </c>
       <c r="G8" s="53" t="n">
-        <v>180.9017117876057</v>
+        <v>154.2285680416316</v>
       </c>
       <c r="H8" s="53" t="n">
-        <v>173.6329296916036</v>
+        <v>148.0917992896102</v>
       </c>
     </row>
     <row r="9">
@@ -1290,25 +1290,25 @@
         <v>17</v>
       </c>
       <c r="B9" s="53" t="n">
-        <v>233.8414002251215</v>
+        <v>198.8600136095933</v>
       </c>
       <c r="C9" s="53" t="n">
-        <v>224.0940874866147</v>
+        <v>190.6372455100842</v>
       </c>
       <c r="D9" s="53" t="n">
-        <v>214.8128607623715</v>
+        <v>182.8068862646378</v>
       </c>
       <c r="E9" s="53" t="n">
-        <v>205.9732306936824</v>
+        <v>175.348338004068</v>
       </c>
       <c r="F9" s="53" t="n">
-        <v>197.5521039203718</v>
+        <v>168.2421763722717</v>
       </c>
       <c r="G9" s="53" t="n">
-        <v>189.5276974701141</v>
+        <v>161.4700785843805</v>
       </c>
       <c r="H9" s="53" t="n">
-        <v>181.8794587600744</v>
+        <v>155.0147562000895</v>
       </c>
     </row>
     <row r="10">
@@ -1316,25 +1316,25 @@
         <v>18</v>
       </c>
       <c r="B10" s="53" t="n">
-        <v>244.6766014965118</v>
+        <v>207.9561595026576</v>
       </c>
       <c r="C10" s="53" t="n">
-        <v>234.4419312946491</v>
+        <v>199.3242550633867</v>
       </c>
       <c r="D10" s="53" t="n">
-        <v>224.6973517571107</v>
+        <v>191.1049113695551</v>
       </c>
       <c r="E10" s="53" t="n">
-        <v>215.4170894663376</v>
+        <v>183.276452585233</v>
       </c>
       <c r="F10" s="53" t="n">
-        <v>206.5768410828878</v>
+        <v>175.8184385773457</v>
       </c>
       <c r="G10" s="53" t="n">
-        <v>198.1536831526224</v>
+        <v>168.7115891271294</v>
       </c>
       <c r="H10" s="53" t="n">
-        <v>190.1259878285452</v>
+        <v>161.9377131105688</v>
       </c>
     </row>
     <row r="11">
@@ -1342,25 +1342,25 @@
         <v>19</v>
       </c>
       <c r="B11" s="53" t="n">
-        <v>255.5118027679022</v>
+        <v>217.0523053957219</v>
       </c>
       <c r="C11" s="53" t="n">
-        <v>244.7897751026835</v>
+        <v>208.0112646166891</v>
       </c>
       <c r="D11" s="53" t="n">
-        <v>234.58184275185</v>
+        <v>199.4029364744724</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>224.8609482389929</v>
+        <v>191.204567166398</v>
       </c>
       <c r="F11" s="53" t="n">
-        <v>215.6015782454038</v>
+        <v>183.3947007824197</v>
       </c>
       <c r="G11" s="53" t="n">
-        <v>206.7796688351307</v>
+        <v>175.9530996698784</v>
       </c>
       <c r="H11" s="53" t="n">
-        <v>198.372516897016</v>
+        <v>168.8606700210482</v>
       </c>
     </row>
     <row r="13">
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="I8" s="48" t="n">
-        <v>0.8558560351311875</v>
+        <v>0.8534843289314809</v>
       </c>
       <c r="K8" s="25">
         <f>MAX(-0.05,NORMINV(RAND(),$C$6,$D$6))</f>
@@ -24571,7 +24571,7 @@
         </is>
       </c>
       <c r="B49" s="20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
@@ -24723,13 +24723,13 @@
         </is>
       </c>
       <c r="B58" s="28" t="n">
-        <v>196.5293719210271</v>
+        <v>167.4202234229029</v>
       </c>
       <c r="C58" s="28" t="n">
-        <v>272.3189371504696</v>
+        <v>226.7350722053176</v>
       </c>
       <c r="D58" s="28" t="n">
-        <v>139.1405551399359</v>
+        <v>121.3158591801177</v>
       </c>
     </row>
     <row r="59">
